--- a/consent_forms/020_treasury_analysis_publication_consent_form--consent_forms.xlsx
+++ b/consent_forms/020_treasury_analysis_publication_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -884,8 +884,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'analyst'}</t>
+          <t>analyst</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Analyst'}</t>
+          <t>Analyst</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'docx'}</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'docx'}</t>
+          <t>docx</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
